--- a/artfynd/A 16133-2023 artfynd.xlsx
+++ b/artfynd/A 16133-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,6 +2419,121 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr">
+        <is>
+          <t>MBD0019 OLP3 Skavsta bibana naturinventeringar 2019</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>91510342</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56133</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100015</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Barbastella barbastellus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Övre Kvistberga, Minninge, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>612021</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6515533</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2019-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Lindén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mattias Stahre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>MBD0019 OLP3 Skavsta bibana naturinventeringar 2019</t>
         </is>

--- a/artfynd/A 16133-2023 artfynd.xlsx
+++ b/artfynd/A 16133-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
